--- a/tabtools/qa/output/tablex_numfmt_t7.xlsx
+++ b/tabtools/qa/output/tablex_numfmt_t7.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="14">
   <si>
     <t>Table</t>
   </si>
@@ -61,10 +61,390 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="90">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="179">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -455,7 +835,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="129">
     <border>
       <left/>
       <right/>
@@ -887,11 +1267,435 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -1134,6 +1938,250 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1149,92 +2197,92 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="3" customWidth="true"/>
-    <col min="3" max="4" width="15.7109375" style="4" customWidth="true"/>
+    <col min="1" max="1" width="2.7109375" style="66" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="67" customWidth="true"/>
+    <col min="3" max="4" width="15.7109375" style="68" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="21" t="s">
+    <row r="1" s="65" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="85" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="112" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="113" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="57">
+      <c r="C4" s="121">
         <v>6072.4230769230771</v>
       </c>
-      <c r="D4" s="58">
+      <c r="D4" s="122">
         <v>19.82692307692308</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="124">
         <v>6384.681818181818</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="125">
         <v>24.77272727272727</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="127">
         <v>6165.2567567567567</v>
       </c>
-      <c r="D6" s="64">
+      <c r="D6" s="128">
         <v>21.297297297297298</v>
       </c>
     </row>
